--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 07/01. Báo giá bảo hành/BG_.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 07\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF85ABDC-04AF-4C5B-A40D-45D81DC1FEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A32834-5C05-4DA5-8425-886DD95130C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t xml:space="preserve">STT </t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>Model/ Mã linh kiện</t>
+  </si>
+  <si>
+    <t>Ghi chú</t>
+  </si>
+  <si>
+    <t>Ghi lại thông tin trạng thái báo giá ví dụ: đã thanh toán cho ai, ghi công nợ cho ai, đang chờ phản hồi, nếu báo giá không có thông tin trong tháng sẽ được đẩy sang tháng có phản hồi</t>
   </si>
 </sst>
 </file>
@@ -111,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="@*."/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -205,6 +211,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -370,7 +382,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -458,6 +470,48 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -515,47 +569,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -929,7 +947,8 @@
     <col min="8" max="8" width="11.7109375" style="3" customWidth="1" outlineLevel="1"/>
     <col min="9" max="9" width="12.140625" style="3" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="12.5703125" style="3" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="1"/>
+    <col min="11" max="11" width="26.28515625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" style="1"/>
     <col min="13" max="14" width="11.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="25" width="9.140625" style="1"/>
     <col min="26" max="26" width="14" style="1" customWidth="1"/>
@@ -938,82 +957,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31"/>
-      <c r="B1" s="32"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="41" t="s">
+      <c r="A1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="38" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="40"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="44" t="s">
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="46"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="47" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="49"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="50" t="s">
+      <c r="A5" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="20"/>
@@ -1024,11 +1043,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1038,11 +1057,11 @@
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
@@ -1055,11 +1074,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="54" t="s">
+      <c r="A9" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1100,27 +1119,33 @@
       <c r="J10" s="24" t="s">
         <v>19</v>
       </c>
+      <c r="K10" s="64" t="s">
+        <v>26</v>
+      </c>
       <c r="AA10" s="2"/>
     </row>
-    <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="60"/>
+    <row r="11" spans="1:27" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="31"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="15"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
       <c r="I11" s="12"/>
       <c r="J11" s="12"/>
+      <c r="K11" s="65" t="s">
+        <v>27</v>
+      </c>
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
-      <c r="C12" s="59"/>
-      <c r="D12" s="59"/>
-      <c r="E12" s="60"/>
+      <c r="A12" s="31"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="15"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
@@ -1128,7 +1153,7 @@
       <c r="J12" s="12"/>
       <c r="AA12" s="2"/>
     </row>
-    <row r="13" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" s="7"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -1155,17 +1180,17 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="61" t="s">
+      <c r="A15" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="62"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="62"/>
-      <c r="I15" s="63"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="35"/>
       <c r="J15" s="29"/>
       <c r="AA15" s="2"/>
     </row>
@@ -1196,37 +1221,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="57" t="s">
+      <c r="A18" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="9"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="57"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="58" t="s">
+      <c r="A19" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
       <c r="E19" s="11"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1297,18 +1322,18 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="56" t="s">
+      <c r="A25" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="10"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="16"/>
       <c r="AA25" s="2"/>
     </row>
@@ -1386,6 +1411,16 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="17">
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A18:D18"/>
@@ -1393,16 +1428,6 @@
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
